--- a/results/tables/18_final_WCB.xlsx
+++ b/results/tables/18_final_WCB.xlsx
@@ -12,27 +12,33 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t xml:space="preserve">Method</t>
   </si>
   <si>
-    <t xml:space="preserve">Beta_RRUI</t>
+    <t xml:space="preserve">Beta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test_statistic</t>
   </si>
   <si>
     <t xml:space="preserve">P_value</t>
   </si>
   <si>
-    <t xml:space="preserve">CI_lower</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI_upper</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rademacher</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Webb</t>
+    <t xml:space="preserve">P_value_strict</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N_draws</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N_ties</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rademacher (exact, 2^G)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Webb (exact, 6^G)</t>
   </si>
 </sst>
 </file>
@@ -377,39 +383,57 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.0179142524069589</v>
+        <v>-0.0171577292272535</v>
       </c>
       <c r="C2" t="n">
+        <v>-1.89510081493448</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="E2" t="n">
         <v>0.0625</v>
       </c>
-      <c r="D2" t="n">
-        <v>-0.0480552671106231</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.00530028556022467</v>
+      <c r="F2" t="n">
+        <v>32</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-0.0171577292272535</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-1.89510081493448</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.131172839506173</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.130401234567901</v>
+      </c>
+      <c r="F3" t="n">
+        <v>7776</v>
+      </c>
+      <c r="G3" t="n">
         <v>6</v>
-      </c>
-      <c r="B3" t="n">
-        <v>-0.0179142524069589</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.119411941194119</v>
-      </c>
-      <c r="D3" t="n">
-        <v>-0.0584661803792643</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.00588513774717334</v>
       </c>
     </row>
   </sheetData>
